--- a/data/trans_orig/IP1015-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1015-Edad-trans_orig.xlsx
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>247724</t>
+          <t>248197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253085</t>
+          <t>253082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501365</t>
+          <t>501416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506289</t>
+          <t>506292</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>717150</t>
+          <t>716925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722027</t>
+          <t>722026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1397488</t>
+          <t>1398189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1403049</t>
+          <t>1403721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143622</t>
+          <t>143828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288359</t>
+          <t>288614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263310</t>
+          <t>263027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497813</t>
+          <t>497457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173272</t>
+          <t>173455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344782</t>
+          <t>344317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>704759</t>
+          <t>704531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742441</t>
+          <t>742599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747536</t>
+          <t>747538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448903</t>
+          <t>1448811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454385</t>
+          <t>1454383</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>254794</t>
+          <t>253504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>465971</t>
+          <t>464689</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170234</t>
+          <t>168887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343369</t>
+          <t>343126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>740621</t>
+          <t>740067</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1444446</t>
+          <t>1445035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1015-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1015-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,92 +1065,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5559</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1183,67 +1183,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>251682</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>248208</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253087</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>251682</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>248197</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253082</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501416</t>
+          <t>501440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506292</t>
+          <t>506290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,92 +2094,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5775</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720626</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>717166</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722028</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720626</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>716925</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722026</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1398189</t>
+          <t>1398161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1403721</t>
+          <t>1403049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,107 +2669,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2453</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2180</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>145801</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>143828</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>143576</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>422</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288614</t>
+          <t>288061</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4074</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3749</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4119</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>266354</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>262849</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>266354</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>263027</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497457</t>
+          <t>497827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3468,47 +3468,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1294</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4502</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4671</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4977</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>176663</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>173863</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>176663</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>173455</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344317</t>
+          <t>344623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2397</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5543</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746101</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>742708</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>747535</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>706448</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>704531</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>704509</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>746101</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>742599</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>747538</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448811</t>
+          <t>1448660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454383</t>
+          <t>1454387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4557</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3654</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3889</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>254177</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>253504</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464689</t>
+          <t>464924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>718</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>718</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5161</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4222</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173330</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>170418</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>173330</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>168887</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343126</t>
+          <t>343507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,107 +5988,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1364</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4777</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4180</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>743480</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>740008</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>743480</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>740067</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1445035</t>
+          <t>1444289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
